--- a/doc/help_dialogs/Input_files/eventbuttons.xlsx
+++ b/doc/help_dialogs/Input_files/eventbuttons.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="406">
   <si>
     <t xml:space="preserve">EVENT CUSTOM BUTTONS</t>
   </si>
@@ -547,7 +547,7 @@
     <t xml:space="preserve">writeBCD(deviceID,register,value) or writeBCD([deviceID,register,value],..,[deviceID,register,value])</t>
   </si>
   <si>
-    <t xml:space="preserve">write 16bit BCD encoded value to register of device with DeviceID </t>
+    <t xml:space="preserve">write 16bit BCD encoded value to register of device with DeviceID</t>
   </si>
   <si>
     <t xml:space="preserve">writeWord(deviceID,register,value) or writeWord([deviceID,register,value],..,[deviceID,register,value])</t>
@@ -976,6 +976,12 @@
   </si>
   <si>
     <t xml:space="preserve">sets the p-i-d parameters of the PID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pidWeights(&lt;beta&gt;,&lt;gamma&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sets the beta and gamma parameters of the PID</t>
   </si>
   <si>
     <t xml:space="preserve">adjustSV(&lt;float&gt;)</t>
@@ -2152,7 +2158,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C166"/>
+  <dimension ref="A1:C167"/>
   <sheetFormatPr defaultColWidth="9.2734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.73"/>
@@ -3146,15 +3152,15 @@
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="3" t="s">
-        <v>133</v>
+        <v>327</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="3" t="s">
-        <v>328</v>
+        <v>133</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>329</v>
@@ -3162,18 +3168,18 @@
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B124" s="3" t="s">
-        <v>137</v>
+        <v>330</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>138</v>
+        <v>331</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B125" s="3" t="s">
-        <v>330</v>
+        <v>137</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>331</v>
+        <v>138</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3329,17 +3335,17 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="1" t="s">
+      <c r="B145" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="C145" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="C145" s="1" t="s">
+    </row>
+    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="1" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="3" t="s">
         <v>373</v>
       </c>
@@ -3397,15 +3403,15 @@
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B153" s="3" t="s">
-        <v>240</v>
+        <v>387</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B154" s="3" t="s">
-        <v>388</v>
+        <v>240</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>389</v>
@@ -3421,26 +3427,26 @@
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B156" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B157" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>385</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="1" t="s">
+        <v>395</v>
+      </c>
       <c r="B158" s="3" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>396</v>
@@ -3448,69 +3454,77 @@
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B159" s="3" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="B160" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B161" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="C161" s="1" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B161" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B162" s="3" t="s">
-        <v>131</v>
+        <v>401</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>132</v>
+        <v>402</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B163" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B164" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>401</v>
+        <v>134</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B165" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>138</v>
+        <v>403</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B166" s="3" t="s">
-        <v>402</v>
+        <v>137</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>403</v>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B167" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>405</v>
       </c>
     </row>
   </sheetData>

--- a/doc/help_dialogs/Input_files/eventbuttons.xlsx
+++ b/doc/help_dialogs/Input_files/eventbuttons.xlsx
@@ -13,6 +13,9 @@
     <sheet name="Labels" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Commands" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Commands!$C$132</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -1086,7 +1089,7 @@
     <t xml:space="preserve">playbackmode(&lt;int&gt;)</t>
   </si>
   <si>
-    <t xml:space="preserve">sets playback mode to 0: off, 1: time, 2: BT, 3: ET</t>
+    <t xml:space="preserve">sets playback mode to 0: off, 1: time, 2: BT, 3: ET; 4: BT/time; 5: ET/time</t>
   </si>
   <si>
     <t xml:space="preserve">playbackdropmode(&lt;int&gt;)</t>
@@ -1199,7 +1202,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> from {1,2,3,4}</t>
+      <t xml:space="preserve"> from {1,2,3,4}; n=5 toggles the PID SV slider visibility</t>
     </r>
   </si>
   <si>

--- a/doc/help_dialogs/Input_files/eventbuttons.xlsx
+++ b/doc/help_dialogs/Input_files/eventbuttons.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Commands" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Commands!$C$132</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Commands!$C$134</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="410">
   <si>
     <t xml:space="preserve">EVENT CUSTOM BUTTONS</t>
   </si>
@@ -691,6 +691,12 @@
     <t xml:space="preserve">sends &lt;value&gt; to &lt;target&gt; via the Kaleido Serial or Network protocol</t>
   </si>
   <si>
+    <t xml:space="preserve">orbiter(&lt;cmd&gt;[,&lt;value&gt;[,&lt;param&gt;]])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sends &lt;cmd&gt; (1byte in HEX) and optional &lt;value&gt; (0-65535) and &lt;param&gt; (0-255) to Orbiter</t>
+  </si>
+  <si>
     <t xml:space="preserve">shellyrelay(n,b)</t>
   </si>
   <si>
@@ -1003,6 +1009,12 @@
   </si>
   <si>
     <t xml:space="preserve">sets the PID target set value SV given in C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pidSVbuttons(&lt;bool&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toggles the visibility of the PID SV buttons</t>
   </si>
   <si>
     <t xml:space="preserve">pidRS(&lt;rs&gt;)</t>
@@ -2161,7 +2173,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C167"/>
+  <dimension ref="A1:C169"/>
   <sheetFormatPr defaultColWidth="9.2734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.73"/>
@@ -2629,7 +2641,7 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="B59" s="3" t="s">
         <v>213</v>
       </c>
       <c r="C59" s="1" t="s">
@@ -2648,29 +2660,29 @@
       <c r="A61" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="C61" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B62" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="C63" s="1" t="s">
         <v>224</v>
       </c>
     </row>
@@ -2681,11 +2693,11 @@
       <c r="B64" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C64" s="1" t="s">
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="3" t="s">
         <v>228</v>
       </c>
@@ -2766,17 +2778,17 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
+      <c r="B75" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C75" s="1" t="s">
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="3" t="s">
         <v>251</v>
       </c>
@@ -2802,69 +2814,69 @@
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B80" s="3" t="s">
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="C81" s="1" t="s">
-        <v>130</v>
+        <v>260</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="3" t="s">
-        <v>259</v>
+        <v>137</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>260</v>
+        <v>138</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2916,16 +2928,16 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
+      <c r="B93" s="3" t="s">
         <v>273</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>214</v>
+        <v>274</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>216</v>
@@ -2933,40 +2945,40 @@
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>276</v>
+        <v>218</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="C96" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C98" s="1" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2995,18 +3007,18 @@
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="3" t="s">
-        <v>131</v>
+        <v>289</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>132</v>
+        <v>290</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="3" t="s">
-        <v>289</v>
+        <v>131</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>290</v>
+        <v>132</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3163,42 +3175,42 @@
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="3" t="s">
-        <v>133</v>
+        <v>329</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B124" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B125" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>138</v>
+        <v>333</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B127" s="3" t="s">
-        <v>334</v>
+        <v>137</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>335</v>
+        <v>138</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3346,25 +3358,25 @@
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="1" t="s">
+      <c r="B146" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="C146" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B147" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C147" s="1" t="s">
+    </row>
+    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="1" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B148" s="3" t="s">
         <v>377</v>
       </c>
@@ -3414,23 +3426,23 @@
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B154" s="3" t="s">
-        <v>240</v>
+        <v>389</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B155" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B156" s="3" t="s">
-        <v>392</v>
+        <v>242</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>393</v>
@@ -3438,96 +3450,112 @@
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B157" s="3" t="s">
-        <v>249</v>
+        <v>394</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="B158" s="3" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B159" s="3" t="s">
-        <v>397</v>
+        <v>251</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="1" t="s">
+        <v>399</v>
+      </c>
       <c r="B160" s="3" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="B161" s="3" t="s">
-        <v>129</v>
+        <v>401</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>130</v>
+        <v>402</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B162" s="3" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="B163" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B164" s="3" t="s">
-        <v>133</v>
+        <v>405</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>134</v>
+        <v>406</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B165" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>403</v>
+        <v>132</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B166" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B167" s="3" t="s">
-        <v>404</v>
+        <v>135</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B168" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B169" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>409</v>
       </c>
     </row>
   </sheetData>

--- a/doc/help_dialogs/Input_files/eventbuttons.xlsx
+++ b/doc/help_dialogs/Input_files/eventbuttons.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Commands" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Commands!$C$134</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Commands!$C$135</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="412">
   <si>
     <t xml:space="preserve">EVENT CUSTOM BUTTONS</t>
   </si>
@@ -701,6 +701,12 @@
   </si>
   <si>
     <t xml:space="preserve">switches Shelly plug number &lt;n&gt; ON if b is true or 1, and OFF otherwise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">publish(&lt;topic&gt;, &lt;value&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">converts the given data to JSON and publishes it on the MQTT server to the given topic</t>
   </si>
   <si>
     <t xml:space="preserve">Hottop Heater</t>
@@ -2173,7 +2179,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C169"/>
+  <dimension ref="A1:C170"/>
   <sheetFormatPr defaultColWidth="9.2734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.73"/>
@@ -2649,7 +2655,7 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+      <c r="B60" s="3" t="s">
         <v>215</v>
       </c>
       <c r="C60" s="1" t="s">
@@ -2668,29 +2674,29 @@
       <c r="A62" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="C62" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="C63" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="C64" s="1" t="s">
         <v>226</v>
       </c>
     </row>
@@ -2701,11 +2707,11 @@
       <c r="B65" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C65" s="1" t="s">
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="3" t="s">
         <v>230</v>
       </c>
@@ -2786,17 +2792,17 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
+      <c r="B76" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C76" s="1" t="s">
+    </row>
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="3" t="s">
         <v>253</v>
       </c>
@@ -2822,69 +2828,69 @@
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B81" s="3" t="s">
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="C82" s="1" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="3" t="s">
-        <v>261</v>
+        <v>137</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>262</v>
+        <v>138</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2936,16 +2942,16 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
+      <c r="B94" s="3" t="s">
         <v>275</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>216</v>
+        <v>276</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>218</v>
@@ -2953,40 +2959,40 @@
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>278</v>
+        <v>220</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="C98" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C99" s="1" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3015,18 +3021,18 @@
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="3" t="s">
-        <v>131</v>
+        <v>291</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>132</v>
+        <v>292</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="3" t="s">
-        <v>291</v>
+        <v>131</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>292</v>
+        <v>132</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3191,15 +3197,15 @@
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B125" s="3" t="s">
-        <v>133</v>
+        <v>333</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="3" t="s">
-        <v>334</v>
+        <v>133</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>335</v>
@@ -3207,18 +3213,18 @@
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B127" s="3" t="s">
-        <v>137</v>
+        <v>336</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>138</v>
+        <v>337</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B128" s="3" t="s">
-        <v>336</v>
+        <v>137</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>337</v>
+        <v>138</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3374,17 +3380,17 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="1" t="s">
+      <c r="B148" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="C148" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C148" s="1" t="s">
+    </row>
+    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="1" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B149" s="3" t="s">
         <v>379</v>
       </c>
@@ -3442,15 +3448,15 @@
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B156" s="3" t="s">
-        <v>242</v>
+        <v>393</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B157" s="3" t="s">
-        <v>394</v>
+        <v>244</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>395</v>
@@ -3466,26 +3472,26 @@
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B159" s="3" t="s">
-        <v>251</v>
+        <v>398</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="B160" s="3" t="s">
-        <v>391</v>
+        <v>253</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="1" t="s">
+        <v>401</v>
+      </c>
       <c r="B161" s="3" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>402</v>
@@ -3493,69 +3499,77 @@
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B162" s="3" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="B163" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B164" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="C164" s="1" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B164" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B165" s="3" t="s">
-        <v>131</v>
+        <v>407</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>132</v>
+        <v>408</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B166" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B167" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>407</v>
+        <v>134</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B168" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>138</v>
+        <v>409</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B169" s="3" t="s">
-        <v>408</v>
+        <v>137</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>409</v>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B170" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>411</v>
       </c>
     </row>
   </sheetData>
